--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.16529236924341</v>
+        <v>1.976860010002054</v>
       </c>
       <c r="D2" t="n">
-        <v>12.93247061854589</v>
+        <v>2.101526475513707</v>
       </c>
       <c r="E2" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F2" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8505315791443</v>
+        <v>4.038211381610948</v>
       </c>
       <c r="D3" t="n">
-        <v>25.04385251537117</v>
+        <v>4.069626033747815</v>
       </c>
       <c r="E3" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F3" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.50871940633066</v>
+        <v>3.170166903528733</v>
       </c>
       <c r="D4" t="n">
-        <v>19.9666774406795</v>
+        <v>3.244585084110419</v>
       </c>
       <c r="E4" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F4" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.12877394062336</v>
+        <v>1.970925765351297</v>
       </c>
       <c r="D5" t="n">
-        <v>12.56185166252462</v>
+        <v>2.04130089516025</v>
       </c>
       <c r="E5" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F5" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.9147919055822</v>
+        <v>3.398653684657107</v>
       </c>
       <c r="D6" t="n">
-        <v>20.49421782192508</v>
+        <v>3.330310396062826</v>
       </c>
       <c r="E6" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F6" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.324356269792128</v>
+        <v>1.190207893841221</v>
       </c>
       <c r="D7" t="n">
-        <v>6.045596874718041</v>
+        <v>0.9824094921416817</v>
       </c>
       <c r="E7" t="n">
-        <v>6.050118723737385</v>
+        <v>0.9831442926073249</v>
       </c>
       <c r="F7" t="n">
-        <v>6.296330227193177</v>
+        <v>1.023153661918891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
